--- a/RFQ Generator Beta Version/Templates/GA TEMPLATE.xlsx
+++ b/RFQ Generator Beta Version/Templates/GA TEMPLATE.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\source\repos\RFQ Generator Beta Version\RFQ Generator Beta Version\bin\Debug\Templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\source\repos\RFQ Generator Beta Version\RFQ Generator Beta Version\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D0BC6CF-5E21-4A22-95A5-778A05FD54CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F3B2057-CBF2-4781-9398-29451FDEC53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{66DC1F52-B897-42E9-AF72-5B240C1967F6}"/>
   </bookViews>
@@ -16,8 +16,8 @@
     <sheet name="priced" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">priced!$A$1:$H$51</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">priced!$1:$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">priced!$A$1:$H$53</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">priced!$1:$23</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -159,9 +159,6 @@
     <t>_validity</t>
   </si>
   <si>
-    <t>delivery_time</t>
-  </si>
-  <si>
     <t>delivery_point</t>
   </si>
   <si>
@@ -181,6 +178,9 @@
   </si>
   <si>
     <t>GELOMBANG AGRESIF SDN BHD</t>
+  </si>
+  <si>
+    <t>header_delivery_time</t>
   </si>
 </sst>
 </file>
@@ -281,7 +281,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -394,7 +394,137 @@
       <diagonal/>
     </border>
     <border>
+      <left style="dotted">
+        <color indexed="64"/>
+      </left>
+      <right style="dotted">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color indexed="64"/>
+      </left>
+      <right style="dotted">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color indexed="64"/>
       </left>
       <right/>
@@ -403,110 +533,9 @@
       <diagonal/>
     </border>
     <border>
-      <left style="dotted">
+      <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="dotted">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dotted">
-        <color indexed="64"/>
-      </left>
-      <right style="dotted">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dotted">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dotted">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dotted">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right/>
       <top/>
       <bottom style="medium">
@@ -515,49 +544,7 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
+      <left style="dotted">
         <color indexed="64"/>
       </left>
       <right/>
@@ -566,12 +553,45 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="dotted">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
       <right/>
       <top/>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -580,18 +600,35 @@
       <left style="dotted">
         <color indexed="64"/>
       </left>
+      <right style="dotted">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="dotted">
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -604,7 +641,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -644,41 +681,22 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -694,10 +712,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -706,17 +724,14 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="10" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="9" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="14" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -733,44 +748,88 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="13" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="26" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -779,19 +838,19 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1055,13 +1114,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>129540</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>15240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>68580</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>45720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1415,7 +1474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{118CEADF-4368-4C62-B3C7-E3EA54788ADE}">
-  <dimension ref="A1:N54"/>
+  <dimension ref="A1:N56"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.109375" style="1" customWidth="1"/>
@@ -1438,29 +1497,29 @@
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="42" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" s="43"/>
-      <c r="E9" s="40"/>
+      <c r="B9" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="36"/>
+      <c r="E9" s="33"/>
     </row>
     <row r="11" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="52"/>
-      <c r="B11" s="65" t="s">
+      <c r="A11" s="44"/>
+      <c r="B11" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="65"/>
+      <c r="C11" s="73"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="2"/>
-      <c r="G11" s="52"/>
-      <c r="H11" s="52"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="44"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C12" s="3"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B13" s="51" t="s">
+      <c r="B13" s="43" t="s">
         <v>28</v>
       </c>
       <c r="C13" s="4" t="s">
@@ -1480,12 +1539,12 @@
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="7"/>
-      <c r="E15" s="69" t="s">
+      <c r="E15" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="F15" s="70"/>
-      <c r="G15" s="70"/>
-      <c r="H15" s="71"/>
+      <c r="F15" s="78"/>
+      <c r="G15" s="78"/>
+      <c r="H15" s="79"/>
     </row>
     <row r="16" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
@@ -1497,7 +1556,7 @@
       <c r="E16" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F16" s="35" t="s">
+      <c r="F16" s="28" t="s">
         <v>39</v>
       </c>
       <c r="G16" s="9"/>
@@ -1513,8 +1572,8 @@
       <c r="E17" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="F17" s="36" t="s">
-        <v>40</v>
+      <c r="F17" s="29" t="s">
+        <v>47</v>
       </c>
       <c r="H17" s="11"/>
     </row>
@@ -1528,10 +1587,10 @@
       <c r="E18" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F18" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="G18" s="39"/>
+      <c r="F18" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="G18" s="32"/>
       <c r="H18" s="7"/>
     </row>
     <row r="19" spans="1:14" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
@@ -1541,12 +1600,12 @@
       <c r="B19" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="49"/>
+      <c r="C19" s="41"/>
       <c r="D19" s="7"/>
       <c r="E19" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F19" s="35" t="s">
+      <c r="F19" s="28" t="s">
         <v>23</v>
       </c>
       <c r="G19" s="12"/>
@@ -1559,17 +1618,17 @@
       <c r="B20" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C20" s="45"/>
+      <c r="C20" s="38"/>
       <c r="D20" s="7"/>
-      <c r="E20" s="47" t="s">
+      <c r="E20" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="F20" s="48"/>
-      <c r="G20" s="48"/>
-      <c r="H20" s="50"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="42"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B21" s="44"/>
+      <c r="B21" s="37"/>
       <c r="E21" s="13"/>
       <c r="F21" s="13"/>
     </row>
@@ -1581,12 +1640,12 @@
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C23" s="72" t="s">
+      <c r="C23" s="80" t="s">
         <v>9</v>
       </c>
-      <c r="D23" s="73"/>
-      <c r="E23" s="73"/>
-      <c r="F23" s="38"/>
+      <c r="D23" s="81"/>
+      <c r="E23" s="81"/>
+      <c r="F23" s="31"/>
       <c r="G23" s="16" t="s">
         <v>10</v>
       </c>
@@ -1595,261 +1654,294 @@
       </c>
     </row>
     <row r="24" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="18"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="20"/>
+      <c r="A24" s="57"/>
+      <c r="B24" s="58"/>
+      <c r="C24" s="59"/>
       <c r="D24" s="21"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="24"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-      <c r="L24" s="25"/>
-      <c r="M24" s="20"/>
-      <c r="N24" s="20"/>
-    </row>
-    <row r="25" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="26" t="s">
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="60"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="19"/>
+      <c r="K24" s="19"/>
+      <c r="L24" s="23"/>
+      <c r="M24" s="19"/>
+      <c r="N24" s="19"/>
+    </row>
+    <row r="25" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="70"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="71"/>
+      <c r="H25" s="72"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="23"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+    </row>
+    <row r="26" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="61" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="27" t="s">
+      <c r="C26" s="82" t="s">
         <v>43</v>
       </c>
-      <c r="C25" s="74" t="s">
+      <c r="D26" s="83"/>
+      <c r="E26" s="83"/>
+      <c r="F26" s="84"/>
+      <c r="G26" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D25" s="75"/>
-      <c r="E25" s="75"/>
-      <c r="F25" s="76"/>
-      <c r="G25" s="41" t="s">
+      <c r="H26" s="62" t="s">
+        <v>34</v>
+      </c>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="23"/>
+      <c r="M26" s="19"/>
+      <c r="N26" s="19"/>
+    </row>
+    <row r="27" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="61"/>
+      <c r="B27" s="24"/>
+      <c r="C27" s="82"/>
+      <c r="D27" s="83"/>
+      <c r="E27" s="83"/>
+      <c r="F27" s="84"/>
+      <c r="G27" s="34"/>
+      <c r="H27" s="62"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="23"/>
+      <c r="M27" s="19"/>
+      <c r="N27" s="19"/>
+    </row>
+    <row r="28" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="63"/>
+      <c r="B28" s="64"/>
+      <c r="C28" s="65"/>
+      <c r="D28" s="66"/>
+      <c r="E28" s="67"/>
+      <c r="F28" s="67"/>
+      <c r="G28" s="68"/>
+      <c r="H28" s="69"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="23"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+    </row>
+    <row r="29" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="53"/>
+      <c r="B29" s="48"/>
+      <c r="C29" s="49"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="74" t="s">
+        <v>29</v>
+      </c>
+      <c r="F29" s="74"/>
+      <c r="G29" s="74"/>
+      <c r="H29" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="23"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="19"/>
+    </row>
+    <row r="30" spans="1:14" s="45" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="54"/>
+      <c r="B30" s="25"/>
+      <c r="E30" s="75" t="s">
+        <v>30</v>
+      </c>
+      <c r="F30" s="75"/>
+      <c r="G30" s="75"/>
+      <c r="H30" s="56" t="s">
+        <v>33</v>
+      </c>
+      <c r="I30" s="25"/>
+      <c r="J30" s="20"/>
+      <c r="K30" s="23"/>
+      <c r="L30" s="23"/>
+      <c r="M30" s="19"/>
+      <c r="N30" s="19"/>
+    </row>
+    <row r="31" spans="1:14" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="55"/>
+      <c r="B31" s="46"/>
+      <c r="C31" s="47"/>
+      <c r="D31" s="46"/>
+      <c r="E31" s="76" t="s">
+        <v>31</v>
+      </c>
+      <c r="F31" s="76"/>
+      <c r="G31" s="76"/>
+      <c r="H31" s="52" t="s">
         <v>45</v>
       </c>
-      <c r="H25" s="46" t="s">
-        <v>34</v>
-      </c>
-      <c r="I25" s="20"/>
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-      <c r="L25" s="25"/>
-      <c r="M25" s="20"/>
-      <c r="N25" s="20"/>
-    </row>
-    <row r="26" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="26"/>
-      <c r="B26" s="27"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="30"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-      <c r="K26" s="20"/>
-      <c r="L26" s="25"/>
-      <c r="M26" s="20"/>
-      <c r="N26" s="20"/>
-    </row>
-    <row r="27" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="61"/>
-      <c r="B27" s="56"/>
-      <c r="C27" s="57"/>
-      <c r="D27" s="58"/>
-      <c r="E27" s="66" t="s">
-        <v>29</v>
-      </c>
-      <c r="F27" s="66"/>
-      <c r="G27" s="66"/>
-      <c r="H27" s="59" t="s">
-        <v>32</v>
-      </c>
-      <c r="I27" s="20"/>
-      <c r="J27" s="20"/>
-      <c r="K27" s="20"/>
-      <c r="L27" s="25"/>
-      <c r="M27" s="20"/>
-      <c r="N27" s="20"/>
-    </row>
-    <row r="28" spans="1:14" s="53" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="62"/>
-      <c r="B28" s="32"/>
-      <c r="E28" s="67" t="s">
-        <v>30</v>
-      </c>
-      <c r="F28" s="67"/>
-      <c r="G28" s="67"/>
-      <c r="H28" s="64" t="s">
-        <v>33</v>
-      </c>
-      <c r="I28" s="32"/>
-      <c r="J28" s="21"/>
-      <c r="K28" s="25"/>
-      <c r="L28" s="25"/>
-      <c r="M28" s="20"/>
-      <c r="N28" s="20"/>
-    </row>
-    <row r="29" spans="1:14" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="63"/>
-      <c r="B29" s="54"/>
-      <c r="C29" s="55"/>
-      <c r="D29" s="54"/>
-      <c r="E29" s="68" t="s">
-        <v>31</v>
-      </c>
-      <c r="F29" s="68"/>
-      <c r="G29" s="68"/>
-      <c r="H29" s="60" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="32"/>
-      <c r="B30" s="32"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="25"/>
-      <c r="F30" s="25"/>
-      <c r="G30" s="33"/>
-      <c r="H30" s="33"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G31" s="34"/>
-      <c r="H31" s="34"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G32" s="34"/>
-      <c r="H32" s="34"/>
+      <c r="A32" s="25"/>
+      <c r="B32" s="25"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="23"/>
+      <c r="G32" s="26"/>
+      <c r="H32" s="26"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G33" s="34"/>
-      <c r="H33" s="34"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="27"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G34" s="34"/>
-      <c r="H34" s="34"/>
+        <v>24</v>
+      </c>
+      <c r="G34" s="27"/>
+      <c r="H34" s="27"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G35" s="34"/>
-      <c r="H35" s="34"/>
+      <c r="G35" s="27"/>
+      <c r="H35" s="27"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G36" s="34"/>
-      <c r="H36" s="34"/>
+        <v>25</v>
+      </c>
+      <c r="G36" s="27"/>
+      <c r="H36" s="27"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G37" s="34"/>
-      <c r="H37" s="34"/>
+      <c r="G37" s="27"/>
+      <c r="H37" s="27"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G38" s="27"/>
+      <c r="H38" s="27"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G39" s="27"/>
+      <c r="H39" s="27"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G38" s="34"/>
-      <c r="H38" s="34"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G39" s="34"/>
-      <c r="H39" s="34"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G40" s="34"/>
-      <c r="H40" s="34"/>
+      <c r="G40" s="27"/>
+      <c r="H40" s="27"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G41" s="34"/>
-      <c r="H41" s="34"/>
+      <c r="G41" s="27"/>
+      <c r="H41" s="27"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G42" s="34"/>
-      <c r="H42" s="34"/>
+      <c r="G42" s="27"/>
+      <c r="H42" s="27"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G43" s="34"/>
-      <c r="H43" s="34"/>
+      <c r="G43" s="27"/>
+      <c r="H43" s="27"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G44" s="27"/>
+      <c r="H44" s="27"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G45" s="27"/>
+      <c r="H45" s="27"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G44" s="34"/>
-      <c r="H44" s="34"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G45" s="34"/>
-      <c r="H45" s="34"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G46" s="34"/>
-      <c r="H46" s="34"/>
+      <c r="G46" s="27"/>
+      <c r="H46" s="27"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G47" s="34"/>
-      <c r="H47" s="34"/>
+      <c r="G47" s="27"/>
+      <c r="H47" s="27"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G48" s="34"/>
-      <c r="H48" s="34"/>
+      <c r="G48" s="27"/>
+      <c r="H48" s="27"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G49" s="34"/>
-      <c r="H49" s="34"/>
+      <c r="G49" s="27"/>
+      <c r="H49" s="27"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G50" s="34"/>
-      <c r="H50" s="34"/>
+      <c r="G50" s="27"/>
+      <c r="H50" s="27"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G51" s="27"/>
+      <c r="H51" s="27"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G52" s="27"/>
+      <c r="H52" s="27"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G51" s="34"/>
-      <c r="H51" s="34"/>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G52" s="34"/>
-      <c r="H52" s="34"/>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G53" s="34"/>
-      <c r="H53" s="34"/>
+      <c r="G53" s="27"/>
+      <c r="H53" s="27"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G54" s="34"/>
-      <c r="H54" s="34"/>
+      <c r="G54" s="27"/>
+      <c r="H54" s="27"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G55" s="27"/>
+      <c r="H55" s="27"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G56" s="27"/>
+      <c r="H56" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="E27:G27"/>
-    <mergeCell ref="E28:G28"/>
     <mergeCell ref="E29:G29"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="E31:G31"/>
     <mergeCell ref="E15:H15"/>
     <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C27:F27"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0" right="0" top="0.21" bottom="0.4" header="0" footer="0"/>
+  <pageMargins left="0" right="0" top="0.19685039370078741" bottom="0.39370078740157483" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" horizontalDpi="4294967293" verticalDpi="300" r:id="rId1"/>
   <headerFooter alignWithMargins="0">
     <oddFooter>Page &amp;P</oddFooter>

--- a/RFQ Generator Beta Version/Templates/GA TEMPLATE.xlsx
+++ b/RFQ Generator Beta Version/Templates/GA TEMPLATE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\source\repos\RFQ Generator Beta Version\RFQ Generator Beta Version\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F3B2057-CBF2-4781-9398-29451FDEC53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DF21764-E9CE-459D-86B0-42914BF901F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{66DC1F52-B897-42E9-AF72-5B240C1967F6}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="priced" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">priced!$A$1:$H$53</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">priced!$A$1:$H$51</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">priced!$1:$23</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>TO</t>
   </si>
@@ -126,21 +126,9 @@
     <t>Date:</t>
   </si>
   <si>
-    <t xml:space="preserve">SUBTOTAL = </t>
-  </si>
-  <si>
-    <t xml:space="preserve">DISCOUNT = </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOTAL NET  = </t>
-  </si>
-  <si>
     <t>sub_total</t>
   </si>
   <si>
-    <t>_discount</t>
-  </si>
-  <si>
     <t>total_price</t>
   </si>
   <si>
@@ -174,13 +162,13 @@
     <t>unit_price</t>
   </si>
   <si>
-    <t>summary_total_price</t>
-  </si>
-  <si>
     <t>GELOMBANG AGRESIF SDN BHD</t>
   </si>
   <si>
     <t>header_delivery_time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL = </t>
   </si>
 </sst>
 </file>
@@ -281,7 +269,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="31">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -473,46 +461,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -533,17 +481,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="dotted">
         <color indexed="64"/>
       </left>
@@ -626,6 +563,43 @@
         <color indexed="64"/>
       </right>
       <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -641,7 +615,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -745,35 +719,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="13" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -782,51 +728,56 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="26" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="21" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -844,13 +795,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1113,73 +1064,49 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>129540</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
+      <xdr:colOff>30481</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>91441</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>68580</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>45720</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>327661</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>40267</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2248" name="Picture 3">
+        <xdr:cNvPr id="5" name="Picture 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB24A3E2-DA23-17D9-9F4E-9EA2756F412E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AFCA4ECC-0860-3D47-8F89-24674F2B2EBD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm rot="10800000">
-          <a:off x="129540" y="9220200"/>
-          <a:ext cx="967740" cy="731520"/>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="30481" y="8511541"/>
+          <a:ext cx="853440" cy="649866"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -1474,7 +1401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{118CEADF-4368-4C62-B3C7-E3EA54788ADE}">
-  <dimension ref="A1:N56"/>
+  <dimension ref="A1:N54"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.109375" style="1" customWidth="1"/>
@@ -1498,17 +1425,17 @@
     <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="35" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C9" s="36"/>
       <c r="E9" s="33"/>
     </row>
     <row r="11" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="44"/>
-      <c r="B11" s="73" t="s">
+      <c r="B11" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="73"/>
+      <c r="C11" s="66"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="2"/>
@@ -1523,7 +1450,7 @@
         <v>28</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -1535,16 +1462,16 @@
         <v>0</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="7"/>
-      <c r="E15" s="77" t="s">
+      <c r="E15" s="68" t="s">
         <v>19</v>
       </c>
-      <c r="F15" s="78"/>
-      <c r="G15" s="78"/>
-      <c r="H15" s="79"/>
+      <c r="F15" s="69"/>
+      <c r="G15" s="69"/>
+      <c r="H15" s="70"/>
     </row>
     <row r="16" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
@@ -1557,7 +1484,7 @@
         <v>6</v>
       </c>
       <c r="F16" s="28" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G16" s="9"/>
       <c r="H16" s="7"/>
@@ -1573,7 +1500,7 @@
         <v>21</v>
       </c>
       <c r="F17" s="29" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H17" s="11"/>
     </row>
@@ -1588,7 +1515,7 @@
         <v>12</v>
       </c>
       <c r="F18" s="30" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G18" s="32"/>
       <c r="H18" s="7"/>
@@ -1598,7 +1525,7 @@
         <v>4</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C19" s="41"/>
       <c r="D19" s="7"/>
@@ -1616,7 +1543,7 @@
         <v>5</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C20" s="38"/>
       <c r="D20" s="7"/>
@@ -1640,11 +1567,11 @@
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C23" s="80" t="s">
+      <c r="C23" s="71" t="s">
         <v>9</v>
       </c>
-      <c r="D23" s="81"/>
-      <c r="E23" s="81"/>
+      <c r="D23" s="72"/>
+      <c r="E23" s="72"/>
       <c r="F23" s="31"/>
       <c r="G23" s="16" t="s">
         <v>10</v>
@@ -1654,14 +1581,14 @@
       </c>
     </row>
     <row r="24" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="57"/>
-      <c r="B24" s="58"/>
-      <c r="C24" s="59"/>
+      <c r="A24" s="45"/>
+      <c r="B24" s="46"/>
+      <c r="C24" s="47"/>
       <c r="D24" s="21"/>
       <c r="E24" s="21"/>
       <c r="F24" s="21"/>
       <c r="G24" s="22"/>
-      <c r="H24" s="60"/>
+      <c r="H24" s="48"/>
       <c r="I24" s="19"/>
       <c r="J24" s="19"/>
       <c r="K24" s="19"/>
@@ -1670,14 +1597,14 @@
       <c r="N24" s="19"/>
     </row>
     <row r="25" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="70"/>
+      <c r="A25" s="58"/>
       <c r="B25" s="18"/>
       <c r="C25" s="19"/>
       <c r="D25" s="20"/>
       <c r="E25" s="20"/>
       <c r="F25" s="20"/>
-      <c r="G25" s="71"/>
-      <c r="H25" s="72"/>
+      <c r="G25" s="59"/>
+      <c r="H25" s="60"/>
       <c r="I25" s="19"/>
       <c r="J25" s="19"/>
       <c r="K25" s="19"/>
@@ -1686,23 +1613,23 @@
       <c r="N25" s="19"/>
     </row>
     <row r="26" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="61" t="s">
-        <v>41</v>
+      <c r="A26" s="49" t="s">
+        <v>37</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="C26" s="82" t="s">
-        <v>43</v>
-      </c>
-      <c r="D26" s="83"/>
-      <c r="E26" s="83"/>
-      <c r="F26" s="84"/>
+        <v>38</v>
+      </c>
+      <c r="C26" s="73" t="s">
+        <v>39</v>
+      </c>
+      <c r="D26" s="74"/>
+      <c r="E26" s="74"/>
+      <c r="F26" s="75"/>
       <c r="G26" s="34" t="s">
-        <v>44</v>
-      </c>
-      <c r="H26" s="62" t="s">
-        <v>34</v>
+        <v>40</v>
+      </c>
+      <c r="H26" s="50" t="s">
+        <v>30</v>
       </c>
       <c r="I26" s="19"/>
       <c r="J26" s="19"/>
@@ -1712,14 +1639,14 @@
       <c r="N26" s="19"/>
     </row>
     <row r="27" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="61"/>
+      <c r="A27" s="49"/>
       <c r="B27" s="24"/>
-      <c r="C27" s="82"/>
-      <c r="D27" s="83"/>
-      <c r="E27" s="83"/>
-      <c r="F27" s="84"/>
+      <c r="C27" s="73"/>
+      <c r="D27" s="74"/>
+      <c r="E27" s="74"/>
+      <c r="F27" s="75"/>
       <c r="G27" s="34"/>
-      <c r="H27" s="62"/>
+      <c r="H27" s="50"/>
       <c r="I27" s="19"/>
       <c r="J27" s="19"/>
       <c r="K27" s="19"/>
@@ -1728,14 +1655,14 @@
       <c r="N27" s="19"/>
     </row>
     <row r="28" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="63"/>
-      <c r="B28" s="64"/>
-      <c r="C28" s="65"/>
-      <c r="D28" s="66"/>
-      <c r="E28" s="67"/>
-      <c r="F28" s="67"/>
-      <c r="G28" s="68"/>
-      <c r="H28" s="69"/>
+      <c r="A28" s="51"/>
+      <c r="B28" s="52"/>
+      <c r="C28" s="53"/>
+      <c r="D28" s="54"/>
+      <c r="E28" s="55"/>
+      <c r="F28" s="55"/>
+      <c r="G28" s="56"/>
+      <c r="H28" s="57"/>
       <c r="I28" s="19"/>
       <c r="J28" s="19"/>
       <c r="K28" s="19"/>
@@ -1744,17 +1671,17 @@
       <c r="N28" s="19"/>
     </row>
     <row r="29" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="53"/>
-      <c r="B29" s="48"/>
-      <c r="C29" s="49"/>
-      <c r="D29" s="50"/>
-      <c r="E29" s="74" t="s">
+      <c r="A29" s="61"/>
+      <c r="B29" s="62"/>
+      <c r="C29" s="63"/>
+      <c r="D29" s="64"/>
+      <c r="E29" s="67" t="s">
+        <v>43</v>
+      </c>
+      <c r="F29" s="67"/>
+      <c r="G29" s="67"/>
+      <c r="H29" s="65" t="s">
         <v>29</v>
-      </c>
-      <c r="F29" s="74"/>
-      <c r="G29" s="74"/>
-      <c r="H29" s="51" t="s">
-        <v>32</v>
       </c>
       <c r="I29" s="19"/>
       <c r="J29" s="19"/>
@@ -1763,47 +1690,26 @@
       <c r="M29" s="19"/>
       <c r="N29" s="19"/>
     </row>
-    <row r="30" spans="1:14" s="45" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="54"/>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="25"/>
       <c r="B30" s="25"/>
-      <c r="E30" s="75" t="s">
-        <v>30</v>
-      </c>
-      <c r="F30" s="75"/>
-      <c r="G30" s="75"/>
-      <c r="H30" s="56" t="s">
-        <v>33</v>
-      </c>
-      <c r="I30" s="25"/>
-      <c r="J30" s="20"/>
-      <c r="K30" s="23"/>
-      <c r="L30" s="23"/>
-      <c r="M30" s="19"/>
-      <c r="N30" s="19"/>
-    </row>
-    <row r="31" spans="1:14" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="55"/>
-      <c r="B31" s="46"/>
-      <c r="C31" s="47"/>
-      <c r="D31" s="46"/>
-      <c r="E31" s="76" t="s">
-        <v>31</v>
-      </c>
-      <c r="F31" s="76"/>
-      <c r="G31" s="76"/>
-      <c r="H31" s="52" t="s">
-        <v>45</v>
-      </c>
+      <c r="C30" s="19"/>
+      <c r="D30" s="23"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="23"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="26"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G31" s="27"/>
+      <c r="H31" s="27"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="25"/>
-      <c r="B32" s="25"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="23"/>
-      <c r="E32" s="23"/>
-      <c r="F32" s="23"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="26"/>
+      <c r="A32" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G32" s="27"/>
+      <c r="H32" s="27"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G33" s="27"/>
@@ -1811,7 +1717,7 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G34" s="27"/>
       <c r="H34" s="27"/>
@@ -1822,7 +1728,7 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G36" s="27"/>
       <c r="H36" s="27"/>
@@ -1833,7 +1739,7 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G38" s="27"/>
       <c r="H38" s="27"/>
@@ -1843,9 +1749,6 @@
       <c r="H39" s="27"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="G40" s="27"/>
       <c r="H40" s="27"/>
     </row>
@@ -1854,6 +1757,9 @@
       <c r="H41" s="27"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="G42" s="27"/>
       <c r="H42" s="27"/>
     </row>
@@ -1863,7 +1769,7 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G44" s="27"/>
       <c r="H44" s="27"/>
@@ -1873,9 +1779,6 @@
       <c r="H45" s="27"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="G46" s="27"/>
       <c r="H46" s="27"/>
     </row>
@@ -1888,31 +1791,31 @@
       <c r="H48" s="27"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="G49" s="27"/>
       <c r="H49" s="27"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="4" t="s">
+        <v>22</v>
+      </c>
       <c r="G50" s="27"/>
       <c r="H50" s="27"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G51" s="27"/>
       <c r="H51" s="27"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="4" t="s">
-        <v>22</v>
-      </c>
       <c r="G52" s="27"/>
       <c r="H52" s="27"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="G53" s="27"/>
       <c r="H53" s="27"/>
     </row>
@@ -1920,20 +1823,10 @@
       <c r="G54" s="27"/>
       <c r="H54" s="27"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G55" s="27"/>
-      <c r="H55" s="27"/>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G56" s="27"/>
-      <c r="H56" s="27"/>
-    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="6">
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="E29:G29"/>
-    <mergeCell ref="E30:G30"/>
-    <mergeCell ref="E31:G31"/>
     <mergeCell ref="E15:H15"/>
     <mergeCell ref="C23:E23"/>
     <mergeCell ref="C26:F26"/>
